--- a/excel/roset-distribuciones-eirl_ccc.xlsx
+++ b/excel/roset-distribuciones-eirl_ccc.xlsx
@@ -609,16 +609,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106251</v>
+        <v>23731</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+          <t>LIDIA MENKELLY HUAYNA VIERA</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>41421475</t>
+          <t>45285564</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>C001616610</t>
+          <t>C001534357</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>C001616610 - LENGUA LOVERA MARINA DEL ROSARIO</t>
+          <t>C001534357 - MAYTA TURPO YOSSELYN FABIOLA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>S17838754</t>
+          <t>S17856256</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -682,11 +682,11 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>41421475AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>45285564AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -695,7 +695,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -725,16 +725,16 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>85766</v>
+        <v>106251</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LIDIA MENKELLY HUAYNA VIERA</t>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>45285564</t>
+          <t>41421475</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -759,12 +759,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>C004097018</t>
+          <t>C001616610</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>C004097018 - ARANA CURI WALTER CESAR</t>
+          <t>C001616610 - LENGUA LOVERA MARINA DEL ROSARIO</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>S17836024</t>
+          <t>S17838754</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -798,11 +798,11 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>45285564AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>41421475AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -824,7 +824,7 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -841,7 +841,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>23731</v>
+        <v>85766</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -875,12 +875,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>C001534357</t>
+          <t>C004097018</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>C001534357 - MAYTA TURPO YOSSELYN FABIOLA</t>
+          <t>C004097018 - ARANA CURI WALTER CESAR</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>S17856256</t>
+          <t>S17836024</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -940,7 +940,7 @@
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -957,16 +957,16 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>13696</v>
+        <v>77314</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LIDIA MENKELLY HUAYNA VIERA</t>
+          <t>FRANZ JAIME SALAS CARPIO</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>45285564</t>
+          <t>40640722</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>C001046058</t>
+          <t>C004201945</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>C001046058 - PEREZ CALCINA FABIOLA CONCEPCION</t>
+          <t>C004201945 - BUTRON ZEBALLOS BRENDA ISABEL</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1016,11 +1016,11 @@
         <v>46235</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>S17846836</t>
+          <t>S17823825</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1030,11 +1030,11 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>45285564AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Quiere comparar precios antes de comprar</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Ver promociones</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1073,16 +1073,16 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>30442</v>
+        <v>85679</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FRANZ JAIME SALAS CARPIO</t>
+          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>40640722</t>
+          <t>41421475</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>C001522236</t>
+          <t>C004215075</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>C001522236 - PACCO CCACHO ANA</t>
+          <t>C004215075 - QUIHUE URBANO FLORA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>S17811536</t>
+          <t>S17807901</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1146,11 +1146,11 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>41421475AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1189,16 +1189,16 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>43081</v>
+        <v>104995</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FRANZ JAIME SALAS CARPIO</t>
+          <t>LIDIA MENKELLY HUAYNA VIERA</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>40640722</t>
+          <t>45285564</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>C001690117</t>
+          <t>C001733451</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>C001690117 - UCHAMACO SUPO YOHANA MARITZA</t>
+          <t>C001733451 - ARAGON PENALVA NATIVIDAD FELICITAS</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>S17799034</t>
+          <t>S17815533</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1262,11 +1262,11 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>45285564AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>132</v>
+        <v>82</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1298,23 +1298,23 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>58638</v>
+        <v>103993</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JOAO MARTIN DIAZ ALANYA</t>
+          <t>FRANZ JAIME SALAS CARPIO</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>47434577</t>
+          <t>40640722</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>C001726327</t>
+          <t>C003001752</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>C001726327 - ROJAS HUALLPA MARGARITA</t>
+          <t>C003001752 - GALLEGOS RODRIGUEZ ROSALIA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>S17802332</t>
+          <t>S17813134</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1378,11 +1378,11 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>47434577AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>92</v>
+        <v>132</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Quiere comparar precios antes de comprar</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1404,33 +1404,33 @@
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>51025</v>
+        <v>99632</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LIDIA MENKELLY HUAYNA VIERA</t>
+          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>45285564</t>
+          <t>73932836</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1455,12 +1455,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>C001732761</t>
+          <t>C001213618</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>C001732761 - CARDENAS RENDON ANA MARIA</t>
+          <t>C001213618 - FUENTES ALVITES DINA LUZ</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1480,11 +1480,11 @@
         <v>46235</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>S17845833</t>
+          <t>S17804055</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1494,11 +1494,11 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>45285564AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>82</v>
+        <v>5</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1530,14 +1530,14 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>59825</v>
+        <v>97534</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1571,12 +1571,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>C001206495</t>
+          <t>C004213504</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>C001206495 - LAYME SIVANA DE PEZO HILARIA</t>
+          <t>C004213504 - HUAMANI LLICA JUANA TOMASA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>S17811738</t>
+          <t>S17817934</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1636,7 +1636,7 @@
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1653,16 +1653,16 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>77314</v>
+        <v>13696</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FRANZ JAIME SALAS CARPIO</t>
+          <t>LIDIA MENKELLY HUAYNA VIERA</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40640722</t>
+          <t>45285564</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1687,12 +1687,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>C004201945</t>
+          <t>C001046058</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>C004201945 - BUTRON ZEBALLOS BRENDA ISABEL</t>
+          <t>C001046058 - PEREZ CALCINA FABIOLA CONCEPCION</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1712,11 +1712,11 @@
         <v>46235</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>S17823825</t>
+          <t>S17846836</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1726,11 +1726,11 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>45285564AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>132</v>
+        <v>82</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Quiere comparar precios antes de comprar</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>Ver promociones</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1769,16 +1769,16 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>85679</v>
+        <v>30442</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SHADIA RUTH BENDEZU VELASQUEZ</t>
+          <t>FRANZ JAIME SALAS CARPIO</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>41421475</t>
+          <t>40640722</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>C004215075</t>
+          <t>C001522236</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>C004215075 - QUIHUE URBANO FLORA</t>
+          <t>C001522236 - PACCO CCACHO ANA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>S17807901</t>
+          <t>S17811536</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1842,11 +1842,11 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>41421475AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1885,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103993</v>
+        <v>43081</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1919,12 +1919,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>C003001752</t>
+          <t>C001690117</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>C003001752 - GALLEGOS RODRIGUEZ ROSALIA</t>
+          <t>C001690117 - UCHAMACO SUPO YOHANA MARITZA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>S17813134</t>
+          <t>S17799034</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>Quiere comparar precios antes de comprar</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1984,7 +1984,7 @@
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -2001,7 +2001,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104995</v>
+        <v>51025</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2035,12 +2035,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>C001733451</t>
+          <t>C001732761</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>C001733451 - ARAGON PENALVA NATIVIDAD FELICITAS</t>
+          <t>C001732761 - CARDENAS RENDON ANA MARIA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2060,11 +2060,11 @@
         <v>46235</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>S17815533</t>
+          <t>S17845833</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2105,28 +2105,28 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>99632</v>
+        <v>58638</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
+          <t>JOAO MARTIN DIAZ ALANYA</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>73932836</t>
+          <t>47434577</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>C001213618</t>
+          <t>C001726327</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>C001213618 - FUENTES ALVITES DINA LUZ</t>
+          <t>C001726327 - ROJAS HUALLPA MARGARITA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>S17804055</t>
+          <t>S17802332</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2190,11 +2190,11 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>47434577AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R15" t="n">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -2226,14 +2226,14 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>97534</v>
+        <v>59825</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2267,12 +2267,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>C004213504</t>
+          <t>C001206495</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>C004213504 - HUAMANI LLICA JUANA TOMASA</t>
+          <t>C001206495 - LAYME SIVANA DE PEZO HILARIA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>S17817934</t>
+          <t>S17811738</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2332,7 +2332,7 @@
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -2349,7 +2349,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>96449</v>
+        <v>65272</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2383,12 +2383,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>C001645212</t>
+          <t>C004060483</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>C001645212 - PURHUAYA LIMASCCA MARIA ASUNCION</t>
+          <t>C004060483 - TACO CHOQUECOTA ISABEL REYNA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>S17819414</t>
+          <t>S17803909</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>No cuenta con presupuesto disponible en ese momento.</t>
+          <t>Quiere comparar precios antes de comprar</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ver promociones</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2465,16 +2465,16 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>78527</v>
+        <v>56977</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
+          <t>FRANZ JAIME SALAS CARPIO</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>73932836</t>
+          <t>40640722</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>C004209415</t>
+          <t>C001629613</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>C004209415 - TALAVERA ESPINAL MARIA ANGELICA</t>
+          <t>C001629613 - PFOCCORI VILCA JUDITH AMELIA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2524,11 +2524,11 @@
         <v>46235</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>S17788772</t>
+          <t>S17808915</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2538,11 +2538,11 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>5</v>
+        <v>132</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2564,24 +2564,24 @@
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>65272</v>
+        <v>41319</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2615,12 +2615,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>C004060483</t>
+          <t>C001711492</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>C004060483 - TACO CHOQUECOTA ISABEL REYNA</t>
+          <t>C001711492 - VELASC CCALLO ALICIA ZONIA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>S17803909</t>
+          <t>S17810273</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>Ver promociones</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2697,7 +2697,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>56977</v>
+        <v>37747</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2731,12 +2731,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>C001629613</t>
+          <t>C001634211</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>C001629613 - PFOCCORI VILCA JUDITH AMELIA</t>
+          <t>C001634211 - CARLO HUAMAN ROSA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>S17808915</t>
+          <t>S17801760</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Quiere comparar precios antes de comprar</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2796,7 +2796,7 @@
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -2813,7 +2813,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>41319</v>
+        <v>33849</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2847,12 +2847,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>C001711492</t>
+          <t>C001650869</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>C001711492 - VELASC CCALLO ALICIA ZONIA</t>
+          <t>C001650869 - QUISPE BORDA NELLY CORINA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2872,11 +2872,11 @@
         <v>46235</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>S17810273</t>
+          <t>S17787856</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>Quiere comparar precios antes de comprar</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2929,16 +2929,16 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>37747</v>
+        <v>47434</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FRANZ JAIME SALAS CARPIO</t>
+          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>40640722</t>
+          <t>73932836</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2963,12 +2963,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>C001634211</t>
+          <t>C001211794</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>C001634211 - CARLO HUAMAN ROSA</t>
+          <t>C001211794 - ZU IGA ARAOS JIMMY</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2988,11 +2988,11 @@
         <v>46235</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>S17801760</t>
+          <t>S17777867</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3002,11 +3002,11 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>132</v>
+        <v>5</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>Quiere comparar precios antes de comprar</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3028,12 +3028,12 @@
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Confirmar pedido</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3045,16 +3045,16 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>33849</v>
+        <v>27312</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FRANZ JAIME SALAS CARPIO</t>
+          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>40640722</t>
+          <t>73932836</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>C001650869</t>
+          <t>C001612240</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>C001650869 - QUISPE BORDA NELLY CORINA</t>
+          <t>C001612240 - GOMEZ MAYTA HUMER</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>S17787856</t>
+          <t>S17785361</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3118,11 +3118,11 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>132</v>
+        <v>5</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3154,23 +3154,23 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>47434</v>
+        <v>96449</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
+          <t>FRANZ JAIME SALAS CARPIO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>73932836</t>
+          <t>40640722</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>C001211794</t>
+          <t>C001645212</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>C001211794 - ZU IGA ARAOS JIMMY</t>
+          <t>C001645212 - PURHUAYA LIMASCCA MARIA ASUNCION</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3220,11 +3220,11 @@
         <v>46235</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>S17777867</t>
+          <t>S17819414</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3234,11 +3234,11 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>5</v>
+        <v>132</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No cuenta con presupuesto disponible en ese momento.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>Confirmar pedido</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3277,7 +3277,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>27312</v>
+        <v>78527</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -3311,12 +3311,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>C001612240</t>
+          <t>C004209415</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>C001612240 - GOMEZ MAYTA HUMER</t>
+          <t>C004209415 - TALAVERA ESPINAL MARIA ANGELICA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3340,7 +3340,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>S17785361</t>
+          <t>S17788772</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3376,33 +3376,33 @@
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>12062</v>
+        <v>72956</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
+          <t>LIDIA MENKELLY HUAYNA VIERA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>73932836</t>
+          <t>45285564</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>C001202512</t>
+          <t>C004197746</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>C001202512 - MOSCOSO DE CASILLAS EUFEMIA</t>
+          <t>C004197746 - IQUIAPAZA IQUIAPAZA JUSTA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3452,11 +3452,11 @@
         <v>46235</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>S17773398</t>
+          <t>S17738477</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3466,11 +3466,11 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>45285564AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R26" t="n">
-        <v>5</v>
+        <v>82</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>No cuenta con presupuesto disponible en ese momento.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3492,33 +3492,33 @@
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>Agregar productos al carrito</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>10729</v>
+        <v>78773</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
+          <t>FRANZ JAIME SALAS CARPIO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>73932836</t>
+          <t>40640722</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>C001210963</t>
+          <t>C004174104</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>C001210963 - POSTIGO GALINDO MAGALI</t>
+          <t>C004174104 - HUAMAN SANCHEZ ROSARIO JULIANA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3568,11 +3568,11 @@
         <v>46235</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>S17743013</t>
+          <t>S17802203</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3582,11 +3582,11 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>5</v>
+        <v>132</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Quiere comparar precios antes de comprar</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3608,7 +3608,7 @@
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
@@ -3625,16 +3625,16 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>22641</v>
+        <v>74977</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LIDIA MENKELLY HUAYNA VIERA</t>
+          <t>FRANZ JAIME SALAS CARPIO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>45285564</t>
+          <t>40640722</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>C001421558</t>
+          <t>C004175646</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>C001421558 - YUPANQUI PUMA FRANCISCA</t>
+          <t>C004175646 - RODRIGUEZ QUISPE WALTER JESUS</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3684,11 +3684,11 @@
         <v>46235</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>S17734203</t>
+          <t>S17821050</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3698,11 +3698,11 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>45285564AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R28" t="n">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>Quiere comparar precios antes de comprar</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3724,12 +3724,12 @@
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3741,16 +3741,16 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>33820</v>
+        <v>92491</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FRANZ JAIME SALAS CARPIO</t>
+          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>40640722</t>
+          <t>73932836</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3765,22 +3765,22 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere pedir con su vendedor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>C001638885</t>
+          <t>C004191972</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>C001638885 - CCAHUATA CCAPATINTA KARINA</t>
+          <t>C004191972 - ANCO PACHAO DE MAYTA YRMA ENCARNACION</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3800,11 +3800,11 @@
         <v>46235</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>S17807057</t>
+          <t>S17777609</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3814,11 +3814,11 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R29" t="n">
-        <v>132</v>
+        <v>5</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>Quiere comparar precios antes de comprar</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3838,35 +3838,23 @@
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>Algo dispuesto</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>38404</v>
+        <v>84472</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LIDIA MENKELLY HUAYNA VIERA</t>
+          <t>FRANZ JAIME SALAS CARPIO</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>45285564</t>
+          <t>40640722</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3891,12 +3879,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>C001707716</t>
+          <t>C004022013</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>C001707716 - MAMANI QUISPE JULIA</t>
+          <t>C004022013 - CHAIÑA AROCUTIPA AMELIA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3916,11 +3904,11 @@
         <v>46235</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>S17848583</t>
+          <t>S17812963</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3930,11 +3918,11 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>45285564AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R30" t="n">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3943,7 +3931,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>Quiere comparar precios antes de comprar</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3956,33 +3944,33 @@
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>57510</v>
+        <v>83361</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FRANZ JAIME SALAS CARPIO</t>
+          <t>LIDIA MENKELLY HUAYNA VIERA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>40640722</t>
+          <t>45285564</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4007,12 +3995,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>C003001703</t>
+          <t>C004184423</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>C003001703 - LOPEZ RAMOS EUSTAQUIA</t>
+          <t>C004184423 - GAMARRA PACCORI FRESIA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4036,7 +4024,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>S17747713</t>
+          <t>S17757203</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4046,11 +4034,11 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>45285564AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R31" t="n">
-        <v>132</v>
+        <v>82</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -4072,33 +4060,33 @@
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>78773</v>
+        <v>108995</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FRANZ JAIME SALAS CARPIO</t>
+          <t>LIDIA MENKELLY HUAYNA VIERA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>40640722</t>
+          <t>45285564</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4123,12 +4111,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>C004174104</t>
+          <t>C001577602</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>C004174104 - HUAMAN SANCHEZ ROSARIO JULIANA</t>
+          <t>C001577602 - CHATA BELIZARIO ROSA AGUSTINA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4148,11 +4136,11 @@
         <v>46235</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>46246</v>
+        <v>46244</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>S17802203</t>
+          <t>S17735969</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4162,11 +4150,11 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>45285564AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R32" t="n">
-        <v>132</v>
+        <v>82</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -4175,7 +4163,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>Quiere comparar precios antes de comprar</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4193,7 +4181,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4205,16 +4193,16 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>74977</v>
+        <v>104904</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FRANZ JAIME SALAS CARPIO</t>
+          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>40640722</t>
+          <t>73932836</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4239,12 +4227,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>C004175646</t>
+          <t>C001649108</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>C004175646 - RODRIGUEZ QUISPE WALTER JESUS</t>
+          <t>C001649108 - ARAUJO PINEDO GLADYS MILAGRITOS</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4268,7 +4256,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>S17821050</t>
+          <t>S17830422</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4278,11 +4266,11 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R33" t="n">
-        <v>132</v>
+        <v>5</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -4304,12 +4292,12 @@
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4321,7 +4309,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>72956</v>
+        <v>102954</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -4355,12 +4343,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>C004197746</t>
+          <t>C001643545</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>C004197746 - IQUIAPAZA IQUIAPAZA JUSTA</t>
+          <t>C001643545 - GOMEZ CARBAJAL MIGUEL OSWALDO</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4380,11 +4368,11 @@
         <v>46235</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>S17738477</t>
+          <t>S17819970</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4407,7 +4395,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4420,7 +4408,7 @@
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
@@ -4430,23 +4418,23 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>92491</v>
+        <v>98021</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
+          <t>LIDIA MENKELLY HUAYNA VIERA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>73932836</t>
+          <t>45285564</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4461,22 +4449,22 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Prefiere pedir con su vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>C004191972</t>
+          <t>C001739425</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>C004191972 - ANCO PACHAO DE MAYTA YRMA ENCARNACION</t>
+          <t>C001739425 - ESTEFANERO VILLANUEVA EDITH ROXANA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4496,11 +4484,11 @@
         <v>46235</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>S17777609</t>
+          <t>S17751276</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4510,11 +4498,11 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>45285564AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R35" t="n">
-        <v>5</v>
+        <v>82</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -4534,14 +4522,26 @@
       <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>Más productos disponibles</t>
+        </is>
+      </c>
       <c r="AB35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>83361</v>
+        <v>99336</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -4575,12 +4575,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>C004184423</t>
+          <t>C004166111</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>C004184423 - GAMARRA PACCORI FRESIA</t>
+          <t>C004166111 - RAMOS OCHOA RUTH LILY</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>S17757203</t>
+          <t>S17762574</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4645,19 +4645,19 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Ver promociones</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>84472</v>
+        <v>94380</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -4691,12 +4691,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>C004022013</t>
+          <t>C004212407</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>C004022013 - CHAIÑA AROCUTIPA AMELIA</t>
+          <t>C004212407 - HUARAYO ARAOS EDITH</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>S17812963</t>
+          <t>S17831578</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4773,16 +4773,16 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>108995</v>
+        <v>12062</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LIDIA MENKELLY HUAYNA VIERA</t>
+          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>45285564</t>
+          <t>73932836</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>C001577602</t>
+          <t>C001202512</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>C001577602 - CHATA BELIZARIO ROSA AGUSTINA</t>
+          <t>C001202512 - MOSCOSO DE CASILLAS EUFEMIA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4832,11 +4832,11 @@
         <v>46235</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>S17735969</t>
+          <t>S17773398</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4846,11 +4846,11 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>45285564AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R38" t="n">
-        <v>82</v>
+        <v>5</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>No cuenta con presupuesto disponible en ese momento.</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4872,12 +4872,12 @@
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Agregar productos al carrito</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4889,7 +4889,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>104904</v>
+        <v>10729</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -4923,12 +4923,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>C001649108</t>
+          <t>C001210963</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>C001649108 - ARAUJO PINEDO GLADYS MILAGRITOS</t>
+          <t>C001210963 - POSTIGO GALINDO MAGALI</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4948,11 +4948,11 @@
         <v>46235</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>46246</v>
+        <v>46244</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>S17830422</t>
+          <t>S17743013</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>Quiere comparar precios antes de comprar</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4993,7 +4993,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5005,7 +5005,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>102954</v>
+        <v>22641</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -5039,12 +5039,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>C001643545</t>
+          <t>C001421558</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>C001643545 - GOMEZ CARBAJAL MIGUEL OSWALDO</t>
+          <t>C001421558 - YUPANQUI PUMA FRANCISCA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5064,11 +5064,11 @@
         <v>46235</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>46246</v>
+        <v>46244</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>S17819970</t>
+          <t>S17734203</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5121,16 +5121,16 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>98021</v>
+        <v>33820</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LIDIA MENKELLY HUAYNA VIERA</t>
+          <t>FRANZ JAIME SALAS CARPIO</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>45285564</t>
+          <t>40640722</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>C001739425</t>
+          <t>C001638885</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>C001739425 - ESTEFANERO VILLANUEVA EDITH ROXANA</t>
+          <t>C001638885 - CCAHUATA CCAPATINTA KARINA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5180,11 +5180,11 @@
         <v>46235</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>S17751276</t>
+          <t>S17807057</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5194,11 +5194,11 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>45285564AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R41" t="n">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Quiere comparar precios antes de comprar</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -5220,24 +5220,24 @@
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>99336</v>
+        <v>38404</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -5271,12 +5271,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>C004166111</t>
+          <t>C001707716</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>C004166111 - RAMOS OCHOA RUTH LILY</t>
+          <t>C001707716 - MAMANI QUISPE JULIA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5296,11 +5296,11 @@
         <v>46235</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>S17762574</t>
+          <t>S17848583</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5341,19 +5341,19 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>Ver promociones</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>94380</v>
+        <v>57510</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -5387,12 +5387,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>C004212407</t>
+          <t>C003001703</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>C004212407 - HUARAYO ARAOS EDITH</t>
+          <t>C003001703 - LOPEZ RAMOS EUSTAQUIA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5412,11 +5412,11 @@
         <v>46235</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>46246</v>
+        <v>46244</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>S17831578</t>
+          <t>S17747713</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>Quiere comparar precios antes de comprar</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5469,7 +5469,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>95832</v>
+        <v>58197</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -5493,22 +5493,22 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Prefiere pedir con su vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>C004192360</t>
+          <t>C001727219</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>C004192360 - MAMANI CALAPUJA MARIA MAGDALENA</t>
+          <t>C001727219 - CHAPI APAZA TRINIDAD REINA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>S17812994</t>
+          <t>S17809631</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5566,23 +5566,35 @@
       <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr"/>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
-      <c r="AA44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>Algo dispuesto</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>Iniciar sesión</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>Apoyo del vendedor</t>
+        </is>
+      </c>
       <c r="AB44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>103349</v>
+        <v>41453</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FRANZ JAIME SALAS CARPIO</t>
+          <t>LIDIA MENKELLY HUAYNA VIERA</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>40640722</t>
+          <t>45285564</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5597,22 +5609,22 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Otros Motivos</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>C003001600</t>
+          <t>C001629600</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>C003001600 - SOTOMAYOR YUCRA NOEMI</t>
+          <t>C001629600 - MAMANI APAZA DE OLAZABAL LUCILA MARIA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5632,11 +5644,11 @@
         <v>46235</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>46242</v>
+        <v>46245</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>S17713056</t>
+          <t>S17775725</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5646,11 +5658,11 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>45285564AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R45" t="n">
-        <v>132</v>
+        <v>82</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -5659,7 +5671,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>Quiere comparar precios antes de comprar</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5670,26 +5682,14 @@
       <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr"/>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>Algo dispuesto</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>Ver promociones</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
       <c r="AB45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>84388</v>
+        <v>39017</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -5723,12 +5723,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>C003001502</t>
+          <t>C001688526</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>C003001502 - SALAZAR CHAVEZ DELIA</t>
+          <t>C001688526 - RIMACHE QUISPE YSIDORA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>S17729628</t>
+          <t>S17711991</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5805,16 +5805,16 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>71414</v>
+        <v>37010</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FRANZ JAIME SALAS CARPIO</t>
+          <t>LIDIA MENKELLY HUAYNA VIERA</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>40640722</t>
+          <t>45285564</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>C003001729</t>
+          <t>C001629305</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>C003001729 - APAZA MALDONADO CLEOFE</t>
+          <t>C001629305 - TONG RUBATTINO LUCIA AMPARO</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5864,11 +5864,11 @@
         <v>46235</v>
       </c>
       <c r="N47" s="3" t="n">
-        <v>46246</v>
+        <v>46242</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>S17812357</t>
+          <t>S17717901</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5878,11 +5878,11 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>45285564AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R47" t="n">
-        <v>132</v>
+        <v>82</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5899,42 +5899,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>Poco dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>Ver promociones</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>71311</v>
+        <v>35070</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>LIDIA MENKELLY HUAYNA VIERA</t>
+          <t>FRANZ JAIME SALAS CARPIO</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>45285564</t>
+          <t>40640722</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5959,12 +5955,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>C004064011</t>
+          <t>C001663140</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>C004064011 - CONDORI ALCAHUAMAN MARILU ERICA</t>
+          <t>C001663140 - CHURQUI HUARSOCCA ROSENIA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5984,11 +5980,11 @@
         <v>46235</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>S17768734</t>
+          <t>S17816485</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5998,11 +5994,11 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>45285564AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R48" t="n">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -6011,7 +6007,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>Quiere comparar precios antes de comprar</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -6024,33 +6020,33 @@
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Ver promociones</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>78329</v>
+        <v>31730</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
+          <t>LIDIA MENKELLY HUAYNA VIERA</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>73932836</t>
+          <t>45285564</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6075,12 +6071,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>C004222298</t>
+          <t>C001628835</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>C004222298 - CHUQUIJA YANA KATY VERONICA</t>
+          <t>C001628835 - CHIPANA PAYEHUANCA CARMEN ROSA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6100,11 +6096,11 @@
         <v>46235</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>46242</v>
+        <v>46245</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>S17720526</t>
+          <t>S17767242</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6114,11 +6110,11 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>45285564AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R49" t="n">
-        <v>5</v>
+        <v>82</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -6145,7 +6141,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>Ver promociones</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6157,7 +6153,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>66716</v>
+        <v>30305</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -6191,12 +6187,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>C004190536</t>
+          <t>C001578682</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>C004190536 - CALCINA CHAMPI CARMEN BEATRIZ</t>
+          <t>C001578682 - CUSI IQUIAPAZA HERLY FROILAN</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6220,7 +6216,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>S17766913</t>
+          <t>S17767843</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6243,7 +6239,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -6256,24 +6252,24 @@
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>Ver promociones</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>58197</v>
+        <v>25401</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -6307,12 +6303,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>C001727219</t>
+          <t>C001480844</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>C001727219 - CHAPI APAZA TRINIDAD REINA</t>
+          <t>C001480844 - CHAVEZ LLAMOCA JENNY DEYSY</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6332,11 +6328,11 @@
         <v>46235</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>46246</v>
+        <v>46242</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>S17809631</t>
+          <t>S17728304</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6359,7 +6355,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>Quiere comparar precios antes de comprar</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -6372,33 +6368,33 @@
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>41453</v>
+        <v>15913</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>LIDIA MENKELLY HUAYNA VIERA</t>
+          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>45285564</t>
+          <t>73932836</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6413,22 +6409,22 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Otros Motivos</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>C001629600</t>
+          <t>C001319463</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>C001629600 - MAMANI APAZA DE OLAZABAL LUCILA MARIA</t>
+          <t>C001319463 - BERMUDEZ CHUI MATILDE FLORENTINA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6448,11 +6444,11 @@
         <v>46235</v>
       </c>
       <c r="N52" s="3" t="n">
-        <v>46245</v>
+        <v>46242</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>S17775725</t>
+          <t>S17718978</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6462,11 +6458,11 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>45285564AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R52" t="n">
-        <v>82</v>
+        <v>5</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -6486,23 +6482,35 @@
       <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr"/>
-      <c r="Y52" t="inlineStr"/>
-      <c r="Z52" t="inlineStr"/>
-      <c r="AA52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>Algo dispuesto</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>Confirmar pedido</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="AB52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>39017</v>
+        <v>11517</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FRANZ JAIME SALAS CARPIO</t>
+          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>40640722</t>
+          <t>73932836</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6527,12 +6535,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>C001688526</t>
+          <t>C001210078</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>C001688526 - RIMACHE QUISPE YSIDORA</t>
+          <t>C001210078 - DURAND FRANCO DINA LUISA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6552,11 +6560,11 @@
         <v>46235</v>
       </c>
       <c r="N53" s="3" t="n">
-        <v>46242</v>
+        <v>46246</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>S17711991</t>
+          <t>S17817068</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6566,11 +6574,11 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R53" t="n">
-        <v>132</v>
+        <v>5</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -6579,7 +6587,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>Quiere comparar precios antes de comprar</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6597,7 +6605,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>Ver promociones</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6609,7 +6617,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>37010</v>
+        <v>4455</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -6633,22 +6641,22 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Otros Motivos</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>C001629305</t>
+          <t>C001034878</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>C001629305 - TONG RUBATTINO LUCIA AMPARO</t>
+          <t>C001034878 - ALVAREZ SUMIRE JOSE ANTONIO</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6668,11 +6676,11 @@
         <v>46235</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>46242</v>
+        <v>46245</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>S17717901</t>
+          <t>S17776232</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6695,7 +6703,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6706,35 +6714,23 @@
       <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr"/>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>Iniciar sesión</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>Más productos disponibles</t>
-        </is>
-      </c>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
       <c r="AB54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>35070</v>
+        <v>95832</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>FRANZ JAIME SALAS CARPIO</t>
+          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>40640722</t>
+          <t>73932836</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6749,22 +6745,22 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere pedir con su vendedor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>C001663140</t>
+          <t>C004192360</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>C001663140 - CHURQUI HUARSOCCA ROSENIA</t>
+          <t>C004192360 - MAMANI CALAPUJA MARIA MAGDALENA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6788,7 +6784,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>S17816485</t>
+          <t>S17812994</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6798,11 +6794,11 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R55" t="n">
-        <v>132</v>
+        <v>5</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -6811,7 +6807,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>Quiere comparar precios antes de comprar</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6822,35 +6818,23 @@
       <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr"/>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>Ver promociones</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
       <c r="AB55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>31730</v>
+        <v>103349</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>LIDIA MENKELLY HUAYNA VIERA</t>
+          <t>FRANZ JAIME SALAS CARPIO</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>45285564</t>
+          <t>40640722</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -6875,12 +6859,12 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>C001628835</t>
+          <t>C003001600</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>C001628835 - CHIPANA PAYEHUANCA CARMEN ROSA</t>
+          <t>C003001600 - SOTOMAYOR YUCRA NOEMI</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6900,11 +6884,11 @@
         <v>46235</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>46245</v>
+        <v>46242</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>S17767242</t>
+          <t>S17713056</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6914,11 +6898,11 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>45285564AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R56" t="n">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -6927,7 +6911,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>Quiere comparar precios antes de comprar</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6940,12 +6924,12 @@
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Ver promociones</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6957,16 +6941,16 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>30305</v>
+        <v>84388</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>LIDIA MENKELLY HUAYNA VIERA</t>
+          <t>FRANZ JAIME SALAS CARPIO</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>45285564</t>
+          <t>40640722</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -6991,12 +6975,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>C001578682</t>
+          <t>C003001502</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>C001578682 - CUSI IQUIAPAZA HERLY FROILAN</t>
+          <t>C003001502 - SALAZAR CHAVEZ DELIA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7016,11 +7000,11 @@
         <v>46235</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>46245</v>
+        <v>46242</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>S17767843</t>
+          <t>S17729628</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7030,11 +7014,11 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>45285564AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R57" t="n">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -7043,7 +7027,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>Quiere comparar precios antes de comprar</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -7056,24 +7040,24 @@
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Ver promociones</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>25401</v>
+        <v>78329</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -7107,12 +7091,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>C001480844</t>
+          <t>C004222298</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>C001480844 - CHAVEZ LLAMOCA JENNY DEYSY</t>
+          <t>C004222298 - CHUQUIJA YANA KATY VERONICA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7136,7 +7120,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>S17728304</t>
+          <t>S17720526</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7159,7 +7143,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>Quiere comparar precios antes de comprar</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -7177,28 +7161,28 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Ver promociones</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>15913</v>
+        <v>71414</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
+          <t>FRANZ JAIME SALAS CARPIO</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>73932836</t>
+          <t>40640722</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7223,12 +7207,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>C001319463</t>
+          <t>C003001729</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>C001319463 - BERMUDEZ CHUI MATILDE FLORENTINA</t>
+          <t>C003001729 - APAZA MALDONADO CLEOFE</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7248,11 +7232,11 @@
         <v>46235</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>46242</v>
+        <v>46246</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>S17718978</t>
+          <t>S17812357</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7262,11 +7246,11 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R59" t="n">
-        <v>5</v>
+        <v>132</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -7275,7 +7259,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -7283,17 +7267,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr"/>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="W59" t="inlineStr"/>
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Poco dispuesto</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>Confirmar pedido</t>
+          <t>Ver promociones</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7305,16 +7293,16 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>11517</v>
+        <v>71311</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
+          <t>LIDIA MENKELLY HUAYNA VIERA</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>73932836</t>
+          <t>45285564</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7339,12 +7327,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>C001210078</t>
+          <t>C004064011</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>C001210078 - DURAND FRANCO DINA LUISA</t>
+          <t>C004064011 - CONDORI ALCAHUAMAN MARILU ERICA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7364,11 +7352,11 @@
         <v>46235</v>
       </c>
       <c r="N60" s="3" t="n">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>S17817068</t>
+          <t>S17768734</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7378,11 +7366,11 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>45285564AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R60" t="n">
-        <v>5</v>
+        <v>82</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -7391,7 +7379,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -7414,14 +7402,14 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>4455</v>
+        <v>66716</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -7445,22 +7433,22 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Otros Motivos</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>C001034878</t>
+          <t>C004190536</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>C001034878 - ALVAREZ SUMIRE JOSE ANTONIO</t>
+          <t>C004190536 - CALCINA CHAMPI CARMEN BEATRIZ</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7484,7 +7472,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>S17776232</t>
+          <t>S17766913</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7507,7 +7495,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7518,23 +7506,35 @@
       <c r="V61" t="inlineStr"/>
       <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
-      <c r="Y61" t="inlineStr"/>
-      <c r="Z61" t="inlineStr"/>
-      <c r="AA61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>Algo dispuesto</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>Ver promociones</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="AB61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>22827</v>
+        <v>77502</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>LIDIA MENKELLY HUAYNA VIERA</t>
+          <t>FRANZ JAIME SALAS CARPIO</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>45285564</t>
+          <t>40640722</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7559,12 +7559,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>C001410269</t>
+          <t>C004205225</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>C001410269 - TIENDAS DE CONVENIENCIA S.A.C.</t>
+          <t>C004205225 - QUISPE ALVIZ MARISOL</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7584,11 +7584,11 @@
         <v>46235</v>
       </c>
       <c r="N62" s="3" t="n">
-        <v>46241</v>
+        <v>46246</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>S17679763</t>
+          <t>S17818475</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7598,11 +7598,11 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>45285564AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R62" t="n">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>Quiere comparar precios antes de comprar</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7624,33 +7624,33 @@
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>28959</v>
+        <v>75407</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
+          <t>FRANZ JAIME SALAS CARPIO</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>73932836</t>
+          <t>40640722</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7675,12 +7675,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>C001623208</t>
+          <t>C004161533</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>C001623208 - QUISPE IQUIAPAZA DIANA ERICA</t>
+          <t>C004161533 - CAYO CAHUI BANI RUBI</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7704,7 +7704,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>S17819277</t>
+          <t>S17820507</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7714,11 +7714,11 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R63" t="n">
-        <v>5</v>
+        <v>132</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>Quiere comparar precios antes de comprar</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7740,7 +7740,7 @@
       <c r="X63" t="inlineStr"/>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
@@ -7750,14 +7750,14 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>30635</v>
+        <v>86900</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -7791,12 +7791,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>C001534138</t>
+          <t>C004206507</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>C001534138 - MAMANI TIPO JENNY VICTORIA</t>
+          <t>C004206507 - LABRA SUCA RENE</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7820,7 +7820,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>S17681788</t>
+          <t>S17686482</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7861,28 +7861,28 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Agregar productos al carrito</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>47748</v>
+        <v>105552</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
+          <t>LIDIA MENKELLY HUAYNA VIERA</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>73932836</t>
+          <t>45285564</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -7907,12 +7907,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>C001726402</t>
+          <t>C001534876</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>C001726402 - CASTILLO CABRERA NILDA</t>
+          <t>C001534876 - GALLEGOS ROQUE PIO</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>S17689357</t>
+          <t>S17684109</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7946,11 +7946,11 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>45285564AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R65" t="n">
-        <v>5</v>
+        <v>82</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7972,12 +7972,12 @@
       <c r="X65" t="inlineStr"/>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7989,7 +7989,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>49887</v>
+        <v>107212</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -8023,12 +8023,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>C003007008</t>
+          <t>C001475791</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>C003007008 - APAZA MELGAREJO LUZ MERIDA</t>
+          <t>C001475791 - HITME MASCA HYDETH</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -8048,11 +8048,11 @@
         <v>46235</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>46241</v>
+        <v>46246</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>S17685603</t>
+          <t>S17820316</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -8093,28 +8093,28 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>Agregar productos al carrito</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>52060</v>
+        <v>96308</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>LIDIA MENKELLY HUAYNA VIERA</t>
+          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>45285564</t>
+          <t>73932836</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8139,12 +8139,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>C001727528</t>
+          <t>C003007052</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>C001727528 - COMERCIAL ALI PANQU E.I.R.L.</t>
+          <t>C003007052 - FERNANDEZ HUAMANI VERONICA EVELLY</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8164,11 +8164,11 @@
         <v>46235</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>46241</v>
+        <v>46246</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>S17695061</t>
+          <t>S17825106</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8178,11 +8178,11 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>45285564AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R67" t="n">
-        <v>82</v>
+        <v>5</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -8209,28 +8209,28 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>Agregar productos al carrito</t>
+          <t>Ver promociones</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>54917</v>
+        <v>111429</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
+          <t>LIDIA MENKELLY HUAYNA VIERA</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>73932836</t>
+          <t>45285564</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>C004008080</t>
+          <t>C001537125</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>C004008080 - TORDOYA HUILLCA ROSA</t>
+          <t>C001537125 - MINIMARKET BERNITA E.I.R.L.</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8284,7 +8284,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>S17691469</t>
+          <t>S17683213</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -8294,11 +8294,11 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>45285564AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R68" t="n">
-        <v>5</v>
+        <v>82</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -8320,33 +8320,33 @@
       <c r="X68" t="inlineStr"/>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>60829</v>
+        <v>22827</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>FRANZ JAIME SALAS CARPIO</t>
+          <t>LIDIA MENKELLY HUAYNA VIERA</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>40640722</t>
+          <t>45285564</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>C004054346</t>
+          <t>C001410269</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>C004054346 - QUISPE AGUILAR GREGORIO</t>
+          <t>C001410269 - TIENDAS DE CONVENIENCIA S.A.C.</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8396,11 +8396,11 @@
         <v>46235</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>46242</v>
+        <v>46241</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>S17718785</t>
+          <t>S17679763</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8410,11 +8410,11 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>45285564AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R69" t="n">
-        <v>132</v>
+        <v>82</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>Quiere comparar precios antes de comprar</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -8436,24 +8436,24 @@
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>Ver promociones</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>59626</v>
+        <v>28959</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -8487,12 +8487,12 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>C003007051</t>
+          <t>C001623208</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>C003007051 - OVIEDO LIMASCCA NELLY ELVIA</t>
+          <t>C001623208 - QUISPE IQUIAPAZA DIANA ERICA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>S17819777</t>
+          <t>S17819277</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8557,28 +8557,28 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Ver promociones</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>75407</v>
+        <v>30635</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FRANZ JAIME SALAS CARPIO</t>
+          <t>LIDIA MENKELLY HUAYNA VIERA</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>40640722</t>
+          <t>45285564</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8603,12 +8603,12 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>C004161533</t>
+          <t>C001534138</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>C004161533 - CAYO CAHUI BANI RUBI</t>
+          <t>C001534138 - MAMANI TIPO JENNY VICTORIA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8628,11 +8628,11 @@
         <v>46235</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>46246</v>
+        <v>46241</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>S17820507</t>
+          <t>S17681788</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -8642,11 +8642,11 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>45285564AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R71" t="n">
-        <v>132</v>
+        <v>82</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>Quiere comparar precios antes de comprar</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8668,33 +8668,33 @@
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>Ver promociones</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>77502</v>
+        <v>47748</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FRANZ JAIME SALAS CARPIO</t>
+          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>40640722</t>
+          <t>73932836</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8719,12 +8719,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>C004205225</t>
+          <t>C001726402</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>C004205225 - QUISPE ALVIZ MARISOL</t>
+          <t>C001726402 - CASTILLO CABRERA NILDA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8744,11 +8744,11 @@
         <v>46235</v>
       </c>
       <c r="N72" s="3" t="n">
-        <v>46246</v>
+        <v>46241</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>S17818475</t>
+          <t>S17689357</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -8758,11 +8758,11 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R72" t="n">
-        <v>132</v>
+        <v>5</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>Quiere comparar precios antes de comprar</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8784,12 +8784,12 @@
       <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8801,16 +8801,16 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>86900</v>
+        <v>49887</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>LIDIA MENKELLY HUAYNA VIERA</t>
+          <t>FRANZ JAIME SALAS CARPIO</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>45285564</t>
+          <t>40640722</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>C004206507</t>
+          <t>C003007008</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>C004206507 - LABRA SUCA RENE</t>
+          <t>C003007008 - APAZA MELGAREJO LUZ MERIDA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>S17686482</t>
+          <t>S17685603</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -8874,11 +8874,11 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>45285564AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R73" t="n">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8900,7 +8900,7 @@
       <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
@@ -8910,14 +8910,14 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>105552</v>
+        <v>52060</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>C001534876</t>
+          <t>C001727528</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>C001534876 - GALLEGOS ROQUE PIO</t>
+          <t>C001727528 - COMERCIAL ALI PANQU E.I.R.L.</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>S17684109</t>
+          <t>S17695061</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -9016,33 +9016,33 @@
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Agregar productos al carrito</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>107212</v>
+        <v>54917</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>FRANZ JAIME SALAS CARPIO</t>
+          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>40640722</t>
+          <t>73932836</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>C001475791</t>
+          <t>C004008080</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>C001475791 - HITME MASCA HYDETH</t>
+          <t>C004008080 - TORDOYA HUILLCA ROSA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9092,11 +9092,11 @@
         <v>46235</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>46246</v>
+        <v>46241</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>S17820316</t>
+          <t>S17691469</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -9106,11 +9106,11 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R75" t="n">
-        <v>132</v>
+        <v>5</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -9119,7 +9119,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -9132,7 +9132,7 @@
       <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
@@ -9142,14 +9142,14 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>96308</v>
+        <v>59626</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -9183,12 +9183,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>C003007052</t>
+          <t>C003007051</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>C003007052 - FERNANDEZ HUAMANI VERONICA EVELLY</t>
+          <t>C003007051 - OVIEDO LIMASCCA NELLY ELVIA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>S17825106</t>
+          <t>S17819777</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -9235,7 +9235,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>Ver promociones</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9265,16 +9265,16 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>111429</v>
+        <v>60829</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>LIDIA MENKELLY HUAYNA VIERA</t>
+          <t>FRANZ JAIME SALAS CARPIO</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>45285564</t>
+          <t>40640722</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>C001537125</t>
+          <t>C004054346</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>C001537125 - MINIMARKET BERNITA E.I.R.L.</t>
+          <t>C004054346 - QUISPE AGUILAR GREGORIO</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -9324,11 +9324,11 @@
         <v>46235</v>
       </c>
       <c r="N77" s="3" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>S17683213</t>
+          <t>S17718785</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -9338,11 +9338,11 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>45285564AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R77" t="n">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>Quiere comparar precios antes de comprar</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -9369,7 +9369,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Ver promociones</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9381,16 +9381,16 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>109972</v>
+        <v>66135</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>FRANZ JAIME SALAS CARPIO</t>
+          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>40640722</t>
+          <t>73932836</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>C004054317</t>
+          <t>C001685939</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>C004054317 - ARGÜELLES QUISPE DIANA BRIGITTE</t>
+          <t>C001685939 - GUEVARA RIMACHE SEBASTIANA</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -9440,11 +9440,11 @@
         <v>46235</v>
       </c>
       <c r="N78" s="3" t="n">
-        <v>46245</v>
+        <v>46239</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>S17767589</t>
+          <t>S17626493</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -9454,11 +9454,11 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R78" t="n">
-        <v>132</v>
+        <v>5</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -9480,12 +9480,12 @@
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Revisar despacho</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9497,7 +9497,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>103734</v>
+        <v>63500</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -9531,12 +9531,12 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>C001715001</t>
+          <t>C004097161</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>C001715001 - CONDORI IQUIAPAZA CLAUDIA</t>
+          <t>C004097161 - MAMANI BELIZARIO VERONICA</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -9556,11 +9556,11 @@
         <v>46235</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>46239</v>
+        <v>46242</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>S17627132</t>
+          <t>S17717449</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -9601,7 +9601,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9613,7 +9613,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>67316</v>
+        <v>63688</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -9637,22 +9637,22 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>No le interesa aprender la app</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>C004099889</t>
+          <t>C004037334</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>C004099889 - PACOMPIA TICONA CESAR ERICK</t>
+          <t>C004037334 - MIRANDA HUARANCCA JULIA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -9672,11 +9672,11 @@
         <v>46235</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>46245</v>
+        <v>46239</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>S17770352</t>
+          <t>S17619844</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9710,23 +9710,35 @@
       <c r="V80" t="inlineStr"/>
       <c r="W80" t="inlineStr"/>
       <c r="X80" t="inlineStr"/>
-      <c r="Y80" t="inlineStr"/>
-      <c r="Z80" t="inlineStr"/>
-      <c r="AA80" t="inlineStr"/>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>Algo dispuesto</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>Agregar productos al carrito</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="AB80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>63500</v>
+        <v>55650</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
+          <t>FRANZ JAIME SALAS CARPIO</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>73932836</t>
+          <t>40640722</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -9751,12 +9763,12 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>C004097161</t>
+          <t>C001730855</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>C004097161 - MAMANI BELIZARIO VERONICA</t>
+          <t>C001730855 - GUTIERREZ PEREZ JANET PAULINA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -9776,11 +9788,11 @@
         <v>46235</v>
       </c>
       <c r="N81" s="3" t="n">
-        <v>46242</v>
+        <v>46245</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>S17717449</t>
+          <t>S17783717</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9790,11 +9802,11 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R81" t="n">
-        <v>5</v>
+        <v>132</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -9803,7 +9815,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>Quiere comparar precios antes de comprar</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9816,12 +9828,12 @@
       <c r="X81" t="inlineStr"/>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Ver promociones</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9833,16 +9845,16 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>66135</v>
+        <v>48258</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
+          <t>FRANZ JAIME SALAS CARPIO</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>73932836</t>
+          <t>40640722</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -9867,12 +9879,12 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>C001685939</t>
+          <t>C001673459</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>C001685939 - GUEVARA RIMACHE SEBASTIANA</t>
+          <t>C001673459 - HUALLPA LAYME BARBARA</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -9892,11 +9904,11 @@
         <v>46235</v>
       </c>
       <c r="N82" s="3" t="n">
-        <v>46239</v>
+        <v>46245</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>S17626493</t>
+          <t>S17781168</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9906,11 +9918,11 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R82" t="n">
-        <v>5</v>
+        <v>132</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -9919,7 +9931,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>Quiere comparar precios antes de comprar</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9932,12 +9944,12 @@
       <c r="X82" t="inlineStr"/>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>Revisar despacho</t>
+          <t>Ver promociones</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9949,7 +9961,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>63688</v>
+        <v>44203</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -9983,12 +9995,12 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>C004037334</t>
+          <t>C001730874</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>C004037334 - MIRANDA HUARANCCA JULIA</t>
+          <t>C001730874 - SALCEDO PUMA CONCEPCION GLORIA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -10008,11 +10020,11 @@
         <v>46235</v>
       </c>
       <c r="N83" s="3" t="n">
-        <v>46239</v>
+        <v>46245</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>S17619844</t>
+          <t>S17768170</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -10035,7 +10047,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Quiere comparar precios antes de comprar</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -10053,28 +10065,28 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>Agregar productos al carrito</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>55650</v>
+        <v>32018</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>FRANZ JAIME SALAS CARPIO</t>
+          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>40640722</t>
+          <t>73932836</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10089,22 +10101,22 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere pedir con su vendedor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>C001730855</t>
+          <t>C001657617</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>C001730855 - GUTIERREZ PEREZ JANET PAULINA</t>
+          <t>C001657617 - CHOQUECHAMBI COAQUIRA NELY FELISA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10124,11 +10136,11 @@
         <v>46235</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>46245</v>
+        <v>46240</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>S17783717</t>
+          <t>S17673087</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -10138,11 +10150,11 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R84" t="n">
-        <v>132</v>
+        <v>5</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -10151,7 +10163,7 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>Quiere comparar precios antes de comprar</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -10162,35 +10174,23 @@
       <c r="V84" t="inlineStr"/>
       <c r="W84" t="inlineStr"/>
       <c r="X84" t="inlineStr"/>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>Algo dispuesto</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>Ver promociones</t>
-        </is>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="Y84" t="inlineStr"/>
+      <c r="Z84" t="inlineStr"/>
+      <c r="AA84" t="inlineStr"/>
       <c r="AB84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>48258</v>
+        <v>28448</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>FRANZ JAIME SALAS CARPIO</t>
+          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>40640722</t>
+          <t>73932836</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10215,12 +10215,12 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>C001673459</t>
+          <t>C001533867</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>C001673459 - HUALLPA LAYME BARBARA</t>
+          <t>C001533867 - MAMANCHOQUE SAICO NIEVES</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -10240,11 +10240,11 @@
         <v>46235</v>
       </c>
       <c r="N85" s="3" t="n">
-        <v>46245</v>
+        <v>46239</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>S17781168</t>
+          <t>S17611600</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -10254,11 +10254,11 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R85" t="n">
-        <v>132</v>
+        <v>5</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>Quiere comparar precios antes de comprar</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -10285,19 +10285,19 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>Ver promociones</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>44203</v>
+        <v>26339</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -10331,12 +10331,12 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>C001730874</t>
+          <t>C001476503</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>C001730874 - SALCEDO PUMA CONCEPCION GLORIA</t>
+          <t>C001476503 - ARANZAMENDI FALCON PEPE CARLOS</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -10356,11 +10356,11 @@
         <v>46235</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>46245</v>
+        <v>46239</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>S17768170</t>
+          <t>S17626913</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -10383,7 +10383,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>Quiere comparar precios antes de comprar</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -10406,23 +10406,23 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>32018</v>
+        <v>26369</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
+          <t>FRANZ JAIME SALAS CARPIO</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>73932836</t>
+          <t>40640722</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10437,22 +10437,22 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Prefiere pedir con su vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>C001657617</t>
+          <t>C001491503</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>C001657617 - CHOQUECHAMBI COAQUIRA NELY FELISA</t>
+          <t>C001491503 - ALVAREZ RIVERA DANITZA LUCIA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10472,11 +10472,11 @@
         <v>46235</v>
       </c>
       <c r="N87" s="3" t="n">
-        <v>46240</v>
+        <v>46245</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>S17673087</t>
+          <t>S17774024</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -10486,11 +10486,11 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R87" t="n">
-        <v>5</v>
+        <v>132</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -10510,23 +10510,35 @@
       <c r="V87" t="inlineStr"/>
       <c r="W87" t="inlineStr"/>
       <c r="X87" t="inlineStr"/>
-      <c r="Y87" t="inlineStr"/>
-      <c r="Z87" t="inlineStr"/>
-      <c r="AA87" t="inlineStr"/>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>Algo dispuesto</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="AB87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>28448</v>
+        <v>5572</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
+          <t>FRANZ JAIME SALAS CARPIO</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>73932836</t>
+          <t>40640722</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10551,12 +10563,12 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>C001533867</t>
+          <t>C001034574</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>C001533867 - MAMANCHOQUE SAICO NIEVES</t>
+          <t>C001034574 - MONRROY MAMANI RINA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -10576,11 +10588,11 @@
         <v>46235</v>
       </c>
       <c r="N88" s="3" t="n">
-        <v>46239</v>
+        <v>46245</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>S17611600</t>
+          <t>S17786769</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -10590,11 +10602,11 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R88" t="n">
-        <v>5</v>
+        <v>132</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -10603,7 +10615,7 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -10621,19 +10633,19 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ver promociones</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>26339</v>
+        <v>109972</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -10667,12 +10679,12 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>C001476503</t>
+          <t>C004054317</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>C001476503 - ARANZAMENDI FALCON PEPE CARLOS</t>
+          <t>C004054317 - ARGÜELLES QUISPE DIANA BRIGITTE</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -10692,11 +10704,11 @@
         <v>46235</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>46239</v>
+        <v>46245</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>S17626913</t>
+          <t>S17767589</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10719,7 +10731,7 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -10749,16 +10761,16 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>26369</v>
+        <v>103734</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>FRANZ JAIME SALAS CARPIO</t>
+          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>40640722</t>
+          <t>73932836</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -10783,12 +10795,12 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>C001491503</t>
+          <t>C001715001</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>C001491503 - ALVAREZ RIVERA DANITZA LUCIA</t>
+          <t>C001715001 - CONDORI IQUIAPAZA CLAUDIA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10808,11 +10820,11 @@
         <v>46235</v>
       </c>
       <c r="N90" s="3" t="n">
-        <v>46245</v>
+        <v>46239</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>S17774024</t>
+          <t>S17627132</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -10822,11 +10834,11 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>40640722AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R90" t="n">
-        <v>132</v>
+        <v>5</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -10848,12 +10860,12 @@
       <c r="X90" t="inlineStr"/>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10865,7 +10877,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>5572</v>
+        <v>67316</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -10889,22 +10901,22 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>No le interesa aprender la app</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>C001034574</t>
+          <t>C004099889</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>C001034574 - MONRROY MAMANI RINA</t>
+          <t>C004099889 - PACOMPIA TICONA CESAR ERICK</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -10928,7 +10940,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>S17786769</t>
+          <t>S17770352</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -10951,7 +10963,7 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -10962,26 +10974,14 @@
       <c r="V91" t="inlineStr"/>
       <c r="W91" t="inlineStr"/>
       <c r="X91" t="inlineStr"/>
-      <c r="Y91" t="inlineStr">
-        <is>
-          <t>Algo dispuesto</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>Ver promociones</t>
-        </is>
-      </c>
-      <c r="AA91" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="Y91" t="inlineStr"/>
+      <c r="Z91" t="inlineStr"/>
+      <c r="AA91" t="inlineStr"/>
       <c r="AB91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>8170</v>
+        <v>71711</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -11005,22 +11005,22 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Otros Motivos</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>C001038606</t>
+          <t>C004160763</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>C001038606 - ZAPANA VILCA DE APAZA MAXIMILIANA</t>
+          <t>C004160763 - RODRIGUEZ PAUCA LUZ MARINA</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -11044,7 +11044,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>S17588223</t>
+          <t>S17601216</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -11067,7 +11067,7 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -11078,26 +11078,14 @@
       <c r="V92" t="inlineStr"/>
       <c r="W92" t="inlineStr"/>
       <c r="X92" t="inlineStr"/>
-      <c r="Y92" t="inlineStr">
-        <is>
-          <t>Algo dispuesto</t>
-        </is>
-      </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>Ninguna, entendió correctamente</t>
-        </is>
-      </c>
-      <c r="AA92" t="inlineStr">
-        <is>
-          <t>Más productos disponibles</t>
-        </is>
-      </c>
+      <c r="Y92" t="inlineStr"/>
+      <c r="Z92" t="inlineStr"/>
+      <c r="AA92" t="inlineStr"/>
       <c r="AB92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>6782</v>
+        <v>70278</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -11131,12 +11119,12 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>C001036315</t>
+          <t>C004159313</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>C001036315 - MASIAS TORRES ISIDORA</t>
+          <t>C004159313 - QUISPE RUELAS YOLANDA SONIA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -11160,7 +11148,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>S17591878</t>
+          <t>S17586571</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -11201,19 +11189,19 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>15288</v>
+        <v>73635</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -11237,22 +11225,22 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere pedir con su vendedor</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>C001318859</t>
+          <t>C004097144</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>C001318859 - CARBAJAL AYA CINTHIA THAIS</t>
+          <t>C004097144 - HUAMANI ALEJO DELFINA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -11276,7 +11264,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>S17587576</t>
+          <t>S17589729</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -11299,7 +11287,7 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -11310,35 +11298,23 @@
       <c r="V94" t="inlineStr"/>
       <c r="W94" t="inlineStr"/>
       <c r="X94" t="inlineStr"/>
-      <c r="Y94" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="AA94" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="Y94" t="inlineStr"/>
+      <c r="Z94" t="inlineStr"/>
+      <c r="AA94" t="inlineStr"/>
       <c r="AB94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>23213</v>
+        <v>78633</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>LIDIA MENKELLY HUAYNA VIERA</t>
+          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>45285564</t>
+          <t>73932836</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11363,12 +11339,12 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>C001475575</t>
+          <t>C004190664</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>C001475575 - CARPIO ZEGARRA GUILLERMO JUBER</t>
+          <t>C004190664 - HUAMANI CCAHUANIHANCCO DEYSI ESPERANZA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -11388,11 +11364,11 @@
         <v>46235</v>
       </c>
       <c r="N95" s="3" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>S17602037</t>
+          <t>S17621775</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -11402,11 +11378,11 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>45285564AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R95" t="n">
-        <v>82</v>
+        <v>5</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -11415,7 +11391,7 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -11445,16 +11421,16 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>27200</v>
+        <v>79949</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
+          <t>LIDIA MENKELLY HUAYNA VIERA</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>73932836</t>
+          <t>45285564</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11479,12 +11455,12 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>C001543568</t>
+          <t>C004161673</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>C001543568 - VILCA ATAMARI LOURDES MIRIAN</t>
+          <t>C004161673 - ZEA CHOQUE IRMA</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -11504,11 +11480,11 @@
         <v>46235</v>
       </c>
       <c r="N96" s="3" t="n">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>S17614972</t>
+          <t>S17593004</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -11518,11 +11494,11 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>45285564AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R96" t="n">
-        <v>5</v>
+        <v>82</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -11531,7 +11507,7 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>Despacho solo permite pago en efectivo</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
@@ -11544,24 +11520,24 @@
       <c r="X96" t="inlineStr"/>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>Ver promociones</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>45109</v>
+        <v>103352</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -11595,12 +11571,12 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>C001708507</t>
+          <t>C004033596</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>C001708507 - HUAMAN CHAMPI FELICIANA</t>
+          <t>C004033596 - UMASI COLQUE MARUJA AURELIA</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11620,11 +11596,11 @@
         <v>46235</v>
       </c>
       <c r="N97" s="3" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>S17585599</t>
+          <t>S17624615</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -11647,7 +11623,7 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -11665,28 +11641,28 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>Confirmar pedido</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>49379</v>
+        <v>103012</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
+          <t>LIDIA MENKELLY HUAYNA VIERA</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>73932836</t>
+          <t>45285564</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -11701,22 +11677,22 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere pedir con su vendedor</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>C001727712</t>
+          <t>C001047731</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>C001727712 - CANARI PUCHO SONIA</t>
+          <t>C001047731 - QUISPE ALVAREZ JUAN DE DIOS</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -11736,11 +11712,11 @@
         <v>46235</v>
       </c>
       <c r="N98" s="3" t="n">
-        <v>46242</v>
+        <v>46238</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>S17709802</t>
+          <t>S17600337</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -11750,11 +11726,11 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>45285564AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R98" t="n">
-        <v>5</v>
+        <v>82</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -11763,7 +11739,7 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
@@ -11774,35 +11750,23 @@
       <c r="V98" t="inlineStr"/>
       <c r="W98" t="inlineStr"/>
       <c r="X98" t="inlineStr"/>
-      <c r="Y98" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>Revisar despacho</t>
-        </is>
-      </c>
-      <c r="AA98" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="Y98" t="inlineStr"/>
+      <c r="Z98" t="inlineStr"/>
+      <c r="AA98" t="inlineStr"/>
       <c r="AB98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>55937</v>
+        <v>95862</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
+          <t>LIDIA MENKELLY HUAYNA VIERA</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>73932836</t>
+          <t>45285564</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -11827,12 +11791,12 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>C003001070</t>
+          <t>C001629121</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>C003001070 - VILLENA VALENCIA EDIT</t>
+          <t>C001629121 - SANCHEZ CONDORI ISABEL GERARDA</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -11852,11 +11816,11 @@
         <v>46235</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>46242</v>
+        <v>46238</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>S17706654</t>
+          <t>S17590228</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -11866,11 +11830,11 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>45285564AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R99" t="n">
-        <v>5</v>
+        <v>82</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -11879,7 +11843,7 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
@@ -11897,28 +11861,28 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>Ver promociones</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>66064</v>
+        <v>111397</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>LIDIA MENKELLY HUAYNA VIERA</t>
+          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>45285564</t>
+          <t>73932836</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -11943,12 +11907,12 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>C004161687</t>
+          <t>C001477029</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>C004161687 - HUARSAYA QUISPE GLADYS PETRONILA</t>
+          <t>C001477029 - ZAPATA HUACHACA NELSON</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -11968,11 +11932,11 @@
         <v>46235</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>S17604158</t>
+          <t>S17620848</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -11982,11 +11946,11 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>45285564AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R100" t="n">
-        <v>82</v>
+        <v>5</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -11995,7 +11959,7 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
@@ -12008,33 +11972,33 @@
       <c r="X100" t="inlineStr"/>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Confirmar pedido</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>78633</v>
+        <v>8170</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
+          <t>LIDIA MENKELLY HUAYNA VIERA</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>73932836</t>
+          <t>45285564</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12059,12 +12023,12 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>C004190664</t>
+          <t>C001038606</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>C004190664 - HUAMANI CCAHUANIHANCCO DEYSI ESPERANZA</t>
+          <t>C001038606 - ZAPANA VILCA DE APAZA MAXIMILIANA</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -12084,11 +12048,11 @@
         <v>46235</v>
       </c>
       <c r="N101" s="3" t="n">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>S17621775</t>
+          <t>S17588223</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -12098,11 +12062,11 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>45285564AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R101" t="n">
-        <v>5</v>
+        <v>82</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -12111,7 +12075,7 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
@@ -12124,7 +12088,7 @@
       <c r="X101" t="inlineStr"/>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
@@ -12134,14 +12098,14 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>79949</v>
+        <v>6782</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -12175,12 +12139,12 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>C004161673</t>
+          <t>C001036315</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>C004161673 - ZEA CHOQUE IRMA</t>
+          <t>C001036315 - MASIAS TORRES ISIDORA</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12204,7 +12168,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>S17593004</t>
+          <t>S17591878</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -12245,7 +12209,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12257,7 +12221,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>70278</v>
+        <v>15288</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -12291,12 +12255,12 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>C004159313</t>
+          <t>C001318859</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>C004159313 - QUISPE RUELAS YOLANDA SONIA</t>
+          <t>C001318859 - CARBAJAL AYA CINTHIA THAIS</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12320,7 +12284,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>S17586571</t>
+          <t>S17587576</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -12343,7 +12307,7 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
@@ -12361,7 +12325,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12373,7 +12337,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>71711</v>
+        <v>23213</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -12397,22 +12361,22 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Otros Motivos</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>C004160763</t>
+          <t>C001475575</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>C004160763 - RODRIGUEZ PAUCA LUZ MARINA</t>
+          <t>C001475575 - CARPIO ZEGARRA GUILLERMO JUBER</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -12436,7 +12400,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>S17601216</t>
+          <t>S17602037</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -12459,7 +12423,7 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
@@ -12470,23 +12434,35 @@
       <c r="V104" t="inlineStr"/>
       <c r="W104" t="inlineStr"/>
       <c r="X104" t="inlineStr"/>
-      <c r="Y104" t="inlineStr"/>
-      <c r="Z104" t="inlineStr"/>
-      <c r="AA104" t="inlineStr"/>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>Ninguna, entendió correctamente</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="AB104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>73635</v>
+        <v>27200</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>LIDIA MENKELLY HUAYNA VIERA</t>
+          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>45285564</t>
+          <t>73932836</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12501,22 +12477,22 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Prefiere pedir con su vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>C004097144</t>
+          <t>C001543568</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>C004097144 - HUAMANI ALEJO DELFINA</t>
+          <t>C001543568 - VILCA ATAMARI LOURDES MIRIAN</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -12536,11 +12512,11 @@
         <v>46235</v>
       </c>
       <c r="N105" s="3" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>S17589729</t>
+          <t>S17614972</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -12550,11 +12526,11 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>45285564AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R105" t="n">
-        <v>82</v>
+        <v>5</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -12563,7 +12539,7 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Despacho solo permite pago en efectivo</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
@@ -12574,14 +12550,26 @@
       <c r="V105" t="inlineStr"/>
       <c r="W105" t="inlineStr"/>
       <c r="X105" t="inlineStr"/>
-      <c r="Y105" t="inlineStr"/>
-      <c r="Z105" t="inlineStr"/>
-      <c r="AA105" t="inlineStr"/>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>Algo dispuesto</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>Ver promociones</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="AB105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>103352</v>
+        <v>45109</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -12615,12 +12603,12 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>C004033596</t>
+          <t>C001708507</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>C004033596 - UMASI COLQUE MARUJA AURELIA</t>
+          <t>C001708507 - HUAMAN CHAMPI FELICIANA</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -12640,11 +12628,11 @@
         <v>46235</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>S17624615</t>
+          <t>S17585599</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -12667,7 +12655,7 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
@@ -12685,28 +12673,28 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Confirmar pedido</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>103012</v>
+        <v>49379</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>LIDIA MENKELLY HUAYNA VIERA</t>
+          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>45285564</t>
+          <t>73932836</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -12721,22 +12709,22 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Prefiere pedir con su vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>C001047731</t>
+          <t>C001727712</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>C001047731 - QUISPE ALVAREZ JUAN DE DIOS</t>
+          <t>C001727712 - CANARI PUCHO SONIA</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -12756,11 +12744,11 @@
         <v>46235</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>46238</v>
+        <v>46242</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>S17600337</t>
+          <t>S17709802</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -12770,11 +12758,11 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>45285564AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R107" t="n">
-        <v>82</v>
+        <v>5</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -12783,7 +12771,7 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
@@ -12794,23 +12782,35 @@
       <c r="V107" t="inlineStr"/>
       <c r="W107" t="inlineStr"/>
       <c r="X107" t="inlineStr"/>
-      <c r="Y107" t="inlineStr"/>
-      <c r="Z107" t="inlineStr"/>
-      <c r="AA107" t="inlineStr"/>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>Revisar despacho</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="AB107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>95862</v>
+        <v>55937</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>LIDIA MENKELLY HUAYNA VIERA</t>
+          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>45285564</t>
+          <t>73932836</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -12835,12 +12835,12 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>C001629121</t>
+          <t>C003001070</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>C001629121 - SANCHEZ CONDORI ISABEL GERARDA</t>
+          <t>C003001070 - VILLENA VALENCIA EDIT</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -12860,11 +12860,11 @@
         <v>46235</v>
       </c>
       <c r="N108" s="3" t="n">
-        <v>46238</v>
+        <v>46242</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>S17590228</t>
+          <t>S17706654</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -12874,11 +12874,11 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>45285564AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R108" t="n">
-        <v>82</v>
+        <v>5</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
@@ -12905,28 +12905,28 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Ver promociones</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>111397</v>
+        <v>66064</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>NAYALIT ALEXANDRA HUAMANI YARO</t>
+          <t>LIDIA MENKELLY HUAYNA VIERA</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>73932836</t>
+          <t>45285564</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -12951,12 +12951,12 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>C001477029</t>
+          <t>C004161687</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>C001477029 - ZAPATA HUACHACA NELSON</t>
+          <t>C004161687 - HUARSAYA QUISPE GLADYS PETRONILA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -12976,11 +12976,11 @@
         <v>46235</v>
       </c>
       <c r="N109" s="3" t="n">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>S17620848</t>
+          <t>S17604158</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -12990,11 +12990,11 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>73932836AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
+          <t>45285564AREQUIPAUTANI SANCHEZ, LAURA EDITH1000036567</t>
         </is>
       </c>
       <c r="R109" t="n">
-        <v>5</v>
+        <v>82</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -13003,7 +13003,7 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
@@ -13016,24 +13016,24 @@
       <c r="X109" t="inlineStr"/>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>Confirmar pedido</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>69749</v>
+        <v>50920</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -13067,12 +13067,12 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>C001707454</t>
+          <t>C003001509</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>C001707454 - SALAZAR QUENAYA CELIA</t>
+          <t>C003001509 - MANUEL HUARACA ROSA</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>S17614571</t>
+          <t>S17628765</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
@@ -13132,7 +13132,7 @@
       <c r="X110" t="inlineStr"/>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z110" t="inlineStr">
@@ -13142,14 +13142,14 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>50920</v>
+        <v>35698</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -13183,12 +13183,12 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>C003001509</t>
+          <t>C001653000</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>C003001509 - MANUEL HUARACA ROSA</t>
+          <t>C001653000 - HUAMANI QUISPE GHANDY LISBETH</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -13208,11 +13208,11 @@
         <v>46235</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>46239</v>
+        <v>46242</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>S17628765</t>
+          <t>S17726918</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -13235,7 +13235,7 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>Está esperando promociones, descuentos o condiciones más favorables.</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
@@ -13248,24 +13248,24 @@
       <c r="X111" t="inlineStr"/>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>Confirmar pedido</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>35698</v>
+        <v>31499</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -13299,12 +13299,12 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>C001653000</t>
+          <t>C001571997</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>C001653000 - HUAMANI QUISPE GHANDY LISBETH</t>
+          <t>C001571997 - BONIFACIO HUAMAN MOISES</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -13324,11 +13324,11 @@
         <v>46235</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>46242</v>
+        <v>46239</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>S17726918</t>
+          <t>S17613216</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -13351,7 +13351,7 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
@@ -13364,7 +13364,7 @@
       <c r="X112" t="inlineStr"/>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z112" t="inlineStr">
@@ -13381,7 +13381,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>31499</v>
+        <v>24964</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -13415,12 +13415,12 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>C001571997</t>
+          <t>C001506810</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>C001571997 - BONIFACIO HUAMAN MOISES</t>
+          <t>C001506810 - HUAHUALUQUE MAMANI VILMA ANTONIA</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -13440,11 +13440,11 @@
         <v>46235</v>
       </c>
       <c r="N113" s="3" t="n">
-        <v>46239</v>
+        <v>46246</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>S17613216</t>
+          <t>S17803159</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -13467,7 +13467,7 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>Quiere comparar precios antes de comprar</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
@@ -13480,12 +13480,12 @@
       <c r="X113" t="inlineStr"/>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13497,7 +13497,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>24964</v>
+        <v>19408</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -13531,12 +13531,12 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>C001506810</t>
+          <t>C001399860</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>C001506810 - HUAHUALUQUE MAMANI VILMA ANTONIA</t>
+          <t>C001399860 - QUISPE CHURA IRENE</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -13556,11 +13556,11 @@
         <v>46235</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>46246</v>
+        <v>46239</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>S17803159</t>
+          <t>S17615714</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -13583,7 +13583,7 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>Quiere comparar precios antes de comprar</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
@@ -13601,19 +13601,19 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Ver promociones</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>19408</v>
+        <v>14560</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -13647,12 +13647,12 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>C001399860</t>
+          <t>C001274552</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>C001399860 - QUISPE CHURA IRENE</t>
+          <t>C001274552 - ZUÑIGA CHOQUE LUZ MARIA</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>S17615714</t>
+          <t>S17612392</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -13699,7 +13699,7 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>Ver promociones</t>
+          <t>Confirmar pedido</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr"/>
@@ -13845,7 +13845,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>14560</v>
+        <v>69749</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -13879,12 +13879,12 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>C001274552</t>
+          <t>C001707454</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>C001274552 - ZUÑIGA CHOQUE LUZ MARIA</t>
+          <t>C001707454 - SALAZAR QUENAYA CELIA</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>S17612392</t>
+          <t>S17614571</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -13961,7 +13961,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>26856</v>
+        <v>91868</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -13995,12 +13995,12 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>C001532731</t>
+          <t>C004059538</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>C001532731 - QUICAÑO ALMANZA ROSA LUZ</t>
+          <t>C004059538 - CHAQUILLA CAYO JOSE ARMANDO</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -14020,11 +14020,11 @@
         <v>46235</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>46238</v>
+        <v>46235</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>S17595789</t>
+          <t>S17533872</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -14047,7 +14047,7 @@
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U118" t="inlineStr">
@@ -14060,12 +14060,12 @@
       <c r="X118" t="inlineStr"/>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -14077,7 +14077,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>28132</v>
+        <v>103872</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -14111,12 +14111,12 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>C001576704</t>
+          <t>C004001762</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>C001576704 - TACO HUAYTA DENIS SILVIA</t>
+          <t>C004001762 - QUISPE ZUÑIGA SILVIA EUGENIA</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -14136,11 +14136,11 @@
         <v>46235</v>
       </c>
       <c r="N119" s="3" t="n">
-        <v>46246</v>
+        <v>46235</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>S17823660</t>
+          <t>S17538564</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -14163,7 +14163,7 @@
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>Prefiere negociar con el vendedor</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U119" t="inlineStr">
@@ -14181,19 +14181,19 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>Ver promociones</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Mejor experiencia con la app</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>41711</v>
+        <v>26856</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -14227,12 +14227,12 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>C001730875</t>
+          <t>C001532731</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>C001730875 - CHUI CALCINA JUDITH</t>
+          <t>C001532731 - QUICAÑO ALMANZA ROSA LUZ</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -14252,11 +14252,11 @@
         <v>46235</v>
       </c>
       <c r="N120" s="3" t="n">
-        <v>46235</v>
+        <v>46238</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>S17531718</t>
+          <t>S17595789</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -14279,7 +14279,7 @@
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U120" t="inlineStr">
@@ -14292,12 +14292,12 @@
       <c r="X120" t="inlineStr"/>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>Confirmar pedido</t>
+          <t>Ninguna, entendió correctamente</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14309,7 +14309,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>62741</v>
+        <v>28132</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -14343,12 +14343,12 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>C004061942</t>
+          <t>C001576704</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>C004061942 - COLQUE CCOLQQUE ROSA</t>
+          <t>C001576704 - TACO HUAYTA DENIS SILVIA</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -14368,11 +14368,11 @@
         <v>46235</v>
       </c>
       <c r="N121" s="3" t="n">
-        <v>46235</v>
+        <v>46246</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>S17537403</t>
+          <t>S17823660</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -14395,7 +14395,7 @@
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere negociar con el vendedor</t>
         </is>
       </c>
       <c r="U121" t="inlineStr">
@@ -14413,7 +14413,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>Confirmar pedido</t>
+          <t>Ver promociones</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14425,7 +14425,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>91868</v>
+        <v>41711</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -14459,12 +14459,12 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>C004059538</t>
+          <t>C001730875</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>C004059538 - CHAQUILLA CAYO JOSE ARMANDO</t>
+          <t>C001730875 - CHUI CALCINA JUDITH</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -14488,7 +14488,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>S17533872</t>
+          <t>S17531718</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -14529,7 +14529,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Confirmar pedido</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14541,7 +14541,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>103872</v>
+        <v>62741</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -14575,12 +14575,12 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>C004001762</t>
+          <t>C004061942</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>C004001762 - QUISPE ZUÑIGA SILVIA EUGENIA</t>
+          <t>C004061942 - COLQUE CCOLQQUE ROSA</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -14604,7 +14604,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>S17538564</t>
+          <t>S17537403</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -14627,7 +14627,7 @@
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U123" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>Ninguna, entendió correctamente</t>
+          <t>Confirmar pedido</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>Mejor experiencia con la app</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr"/>
